--- a/processed_ruby_restored_xlsx/sc032b_３日目：瑠璃千代.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc032b_３日目：瑠璃千代.ss.xlsx
@@ -564,8 +564,8 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Rather, she’d probably feel responsible and keep it on
-her at all times….</t>
+          <t>Rather, she’d probably feel responsible and keep it
+on her at all times….</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -626,8 +626,8 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan might have come back too, but well… it can't
-be helped.</t>
+          <t>Nono-chan might have come back too, but well… it
+can't be helped.</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -642,9 +642,9 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>If it is Nono-chan, on the contrary, I feel like she'd
-act all teacherly and just hand it back if I asked her
-to.</t>
+          <t>If it is Nono-chan, on the contrary, I feel like
+she'd act all teacherly and just hand it back if I
+asked her to.</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1380,9 +1380,9 @@
       <c r="B60" s="1" t="inlineStr">
         <is>
           <t>…Come to think of it, there was that scene where a
-little girl, seeing an electric massager for the first
-time, touches it innocently but still feels her heart
-race.</t>
+little girl, seeing an electric massager for the
+first time, touches it innocently but still feels her
+heart race.</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1741,8 +1741,8 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>Even while feeling guilty, she probably gets turned on
-because she can't help thinking it feels good.</t>
+          <t>Even while feeling guilty, she probably gets turned
+on because she can't help thinking it feels good.</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1849,8 +1849,8 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>...Even seeing that scene makes me feel like I'm doing
-something wrong.</t>
+          <t>...Even seeing that scene makes me feel like I'm
+doing something wrong.</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2098,8 +2098,8 @@
       <c r="B106" s="1" t="inlineStr">
         <is>
           <t>No, you mustn't, she said, and right after that, I
-pressed the smartphone even harder against her between
-(my/her) legs.</t>
+pressed the smartphone even harder against her
+between (my/her) legs.</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2160,8 +2160,8 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>I experienced something I’d seen in manga and realized
-it really was true.</t>
+          <t>I experienced something I’d seen in manga and
+realized it really was true.</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2222,7 +2222,8 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan's voice is getting higher and higher...</t>
+          <t>Rurichiyo-chan's voice is getting higher and
+higher...</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2253,8 +2254,8 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>I wonder if this actually feels good... it seems to be
-satisfying that sort of intellectual curiosity.</t>
+          <t>I wonder if this actually feels good... it seems to
+be satisfying that sort of intellectual curiosity.</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2330,7 +2331,8 @@
       <c r="B121" s="1" t="inlineStr">
         <is>
           <t>Rurichiyo-chan, who doesn't know I'm watching, is
-using my smartphone and getting more and more aroused.</t>
+using my smartphone and getting more and more
+aroused.</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2468,8 +2470,9 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>However, Rurichiyo-chan looked down sadly, and timidly
-moved her smartphone away from between her legs.</t>
+          <t>However, Rurichiyo-chan looked down sadly, and
+timidly moved her smartphone away from between her
+legs.</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2484,7 +2487,8 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>As in the manga, rubbing between my legs feels good…….</t>
+          <t>As in the manga, rubbing between my legs feels
+good…….</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2500,8 +2504,8 @@
       <c r="B132" s="1" t="inlineStr">
         <is>
           <t>I get that, but it seems to have stopped
-Rurichiyo-chan’s original seriousness and modesty from
-making her feel good.</t>
+Rurichiyo-chan’s original seriousness and modesty
+from making her feel good.</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2562,8 +2566,8 @@
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan let out a sigh that carried a different
-intention than before.</t>
+          <t>Rurichiyo-chan let out a sigh that carried a
+different intention than before.</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2578,8 +2582,8 @@
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>Then she put her phone back where it was and hurriedly
-turned on her heel.</t>
+          <t>Then she put her phone back where it was and
+hurriedly turned on her heel.</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2837,8 +2841,8 @@
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>…For someone like Rurichiyo-chan, it’s impossible that
-she’d leave without closing the door.</t>
+          <t>…For someone like Rurichiyo-chan, it’s impossible
+that she’d leave without closing the door.</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2869,7 +2873,8 @@
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>…Still, she’s grown up a little as a girl, hasn’t she.</t>
+          <t>…Still, she’s grown up a little as a girl, hasn’t
+she.</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2884,8 +2889,8 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>Satisfied with that, I pulled myself together and went
-into the room.</t>
+          <t>Satisfied with that, I pulled myself together and
+went into the room.</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2945,8 +2950,8 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>…The Comic RO that Rurichiyo-chan was supposed to have
-brought wasn’t in the room.</t>
+          <t>…The Comic RO that Rurichiyo-chan was supposed to
+have brought wasn’t in the room.</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2961,8 +2966,8 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>She must’ve taken it back with her when she dashed out
-just now.</t>
+          <t>She must’ve taken it back with her when she dashed
+out just now.</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -3023,7 +3028,8 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>There’s absolutely no way I can ask for it back today…</t>
+          <t>There’s absolutely no way I can ask for it back
+today…</t>
         </is>
       </c>
       <c r="C166" t="n">

--- a/processed_ruby_restored_xlsx/sc032b_３日目：瑠璃千代.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc032b_３日目：瑠璃千代.ss.xlsx
@@ -515,9 +515,8 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>She’s the most dependable, so I think everyone would
-figure there’s no mistake in leaving things with
-Rurichiyo-chan.</t>
+          <t>She's the most reliable, so I think everyone would
+agree it's safe to entrust it to Rurichiyo-chan.</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -532,8 +531,8 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Comic RO isn’t a hazardous material, but to everyone
-it’s, in a way, something close to a hazardous thing.</t>
+          <t>Comic RO isn't literally a hazardous material, but to
+everyone it's, in a sense, almost like one.</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -548,8 +547,8 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>And Rurichiyo-chan, if someone entrusted it to her, I
-think she wouldn’t be able to refuse.</t>
+          <t>And Rurichiyo-chan—if everyone entrusted it to her, I
+think she wouldn't be able to say no.</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -564,8 +563,8 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Rather, she’d probably feel responsible and keep it
-on her at all times….</t>
+          <t>Rather, Rurichiyo-chan would probably feel a sense of
+responsibility and carry it with her at all times…</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -595,7 +594,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>But where could Rurichiyo-chan be？</t>
+          <t>But where could Rurichiyo-chan be?</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -689,7 +688,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>「Rurichiyo-chan？ Are you... there？」</t>
+          <t>「Rurichiyo-chan? Are you there...?」</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -765,7 +764,7 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>Maybe neither of them have come back yet...？</t>
+          <t>I wonder if neither of them has come back yet...?</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -795,8 +794,8 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>I sneak around so no one meets me and try to find
-Rurichiyo-chan.</t>
+          <t>I sneak around, trying not to run into anyone, as I
+look for Rurichiyo-chan.</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -826,8 +825,8 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>Even though it's limited to inside the dorm, did we
-just pass each other somewhere？</t>
+          <t>It's only inside the dorm, so could I have missed her
+somewhere?</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -857,7 +856,7 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>「...Hmmm.」</t>
+          <t>「…Hmm...」</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -904,8 +903,7 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>When she came back to her room, the door was half
-open.</t>
+          <t>When I returned to my room, the door was half open.</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -920,8 +918,8 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>Finding it odd, and having a vague hunch, I peeked in
-and Rurichiyo-chan was there.</t>
+          <t>I thought it odd, but on a hunch I peeked in and
+found Rurichiyo-chan.</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -936,7 +934,7 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan has a Comic RO in her hand.</t>
+          <t>Rurichiyo-chan was holding a copy of Comic RO.</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -997,7 +995,7 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>「Ruu...」</t>
+          <t>Ru...</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1028,8 +1026,8 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, though fidgety, is spacing out and
-staring at something.</t>
+          <t>Rurichiyo-chan, though fidgety, was staring blankly
+at something.</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1074,7 +1072,7 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>Wait… is that my phone？</t>
+          <t>Is that... my smartphone?</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1104,7 +1102,7 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>「Nngh… nnnu…」</t>
+          <t>Nngh... nnnh...</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1119,8 +1117,9 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, staring blankly at her smartphone,
-mumbled to herself as she picked it up.</t>
+          <t>Rurichiyo-chan, who had been staring blankly at my
+smartphone, muttered under her breath as she picked
+it up.</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1135,7 +1134,7 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>Then she activates the vibration.</t>
+          <t>Then she switches the phone to vibrate.</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1195,7 +1194,7 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>「Nng… Nnng… Haa…！」</t>
+          <t>「Nng... nnnh... fuu...!」</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1240,8 +1239,8 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, unbelievably, pressed the buzzing
-phone against her between-the-legs.</t>
+          <t>To my astonishment, Rurichiyo-chan pressed the
+vibrating phone between her legs.</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1271,7 +1270,7 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>「Huh... hn... hn...！」</t>
+          <t>「Fuu... nng... nng...！」</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1286,7 +1285,7 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>And then, she begins to let out a muffled sigh….</t>
+          <t>Then she begins to let out a muffled sigh…</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1331,7 +1330,8 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>……No way, Rurichiyo-chan doing something like that…</t>
+          <t>...No way... Rurichiyo-chan would do something like
+that...</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1346,8 +1346,8 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>In my room, with my phone, using a vibrator to
-masturbate…？</t>
+          <t>In my room... using my phone as a vibrator to
+masturbate...?</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1362,9 +1362,9 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>My head feels like it might explode from seeing such
-an utterly unexpected sight, but when I notice Comic
-RO there, I somehow start to understand why.</t>
+          <t>I was bewildered by such an utterly unexpected sight,
+but when I saw a copy of Comic RO there, I somehow
+felt like I understood.</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1398,8 +1398,8 @@
       <c r="B61" s="1" t="inlineStr">
         <is>
           <t>If I remember correctly, the line in that scene was,
-"If I... put this... here, I wonder what would
-happen...？" I think that's what it said.</t>
+"What would happen if I put this... here...?" I think
+that's how it went.</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1430,10 +1430,9 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>No... because it's Rurichiyo-chan, she probably
-remembered how the manga depicted it and, on top of
-that, overlaid the manga girl's situation onto her
-own.</t>
+          <t>No... knowing Rurichiyo-chan, she probably remembered
+how it was portrayed in the manga and overlaid the
+manga girl's situation onto her own.</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1448,7 +1447,7 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>That would suit Rurichiyo-chan... .</t>
+          <t>That's more like Rurichiyo-chan...</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1478,7 +1477,7 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>「...n, nn...」</t>
+          <t>「Nng... nng...」</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1493,8 +1492,8 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan took on a listless expression and
-gently lowered her gaze... .</t>
+          <t>Rurichiyo-chan wore a pensive expression and gently
+lowered her gaze...</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1509,8 +1508,8 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>The manga girl, though driven by curiosity, felt
-ashamed of the act.</t>
+          <t>The girl in the manga, though driven by curiosity,
+felt embarrassed by the act.</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1525,7 +1524,7 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>I guess Rurichiyo-chan is the same.</t>
+          <t>So Rurichiyo-chan is the same after all.</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1540,7 +1539,7 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>This is no good... she must be thinking that.</t>
+          <t>She must be thinking, "I shouldn't be doing this..."</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1570,7 +1569,7 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>「nfu... fu... faa...」</t>
+          <t>「Nfuh... fuh... faaah...」</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1585,9 +1584,9 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>...And yet, whether it's the girl in the manga or
-Rurichiyo-chan, they both feel pleasure from doing
-something they shouldn't.</t>
+          <t>It's the same for the girl in the manga and
+Rurichiyo-chan: both end up feeling aroused from
+doing something they shouldn't.</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1602,8 +1601,8 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan presses a smartphone hard between her
-legs and lets out a hot, muffled breath.</t>
+          <t>Rurichiyo-chan presses my smartphone vigorously
+against her crotch and exhales a hot, muffled breath.</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1633,7 +1632,7 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>「Huh...nng, nnh...n—！」</t>
+          <t>「Fuh... nng, nng... nuu...!」</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1648,7 +1647,7 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan closes her eyes and shrugs her
+          <t>Rurichiyo-chan closes her eyes and hunches her
 shoulders.</t>
         </is>
       </c>
@@ -1664,8 +1663,8 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>The breaths that escape in that position are
-restrained.</t>
+          <t>The breaths she lets out in that position are
+tentative.</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1711,7 +1710,7 @@
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>「Fuu...uuh...uh...fuu...」</t>
+          <t>「Fuu... uuh... ... fuu...」</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1726,7 +1725,7 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>...Yeah, it's that, after all.</t>
+          <t>...So it really is that, huh.</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1757,8 +1756,8 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>Because Rurichiyo-chan is usually so earnest, she can
-vividly feel that difference in temperature herself.</t>
+          <t>Because Rurichiyo-chan is usually so earnest, she
+feels that contrast all the more acutely.</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1773,8 +1772,8 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>To the point where she thinks it's wrong but can't
-stop...！</t>
+          <t>That's exactly it — to the point where she thinks
+it's wrong but can't stop herself...!</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1804,7 +1803,7 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>「...kku, fuu... fuu, fuu...」</t>
+          <t>「...k-k, fuh... fuh, fuh...」</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1849,8 +1848,7 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>...Even seeing that scene makes me feel like I'm
-doing something wrong.</t>
+          <t>...Even I, watching that scene, start to feel guilty.</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1881,8 +1879,8 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>Watching that figure feels horribly immoral... but I
-can't look away...！</t>
+          <t>Seeing her like that feels terribly sinful... but I
+can't look away...!</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1912,7 +1910,7 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>「Nnn... fuh... nngh...！ Haa...！」</t>
+          <t>Nn... fuh... nng...! Haa...!</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1943,7 +1941,7 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>Did you clearly notice that it felt good？</t>
+          <t>Were you clearly aware that it felt good?</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1989,7 +1987,7 @@
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>「Ah... ah... I shouldn't... 」</t>
+          <t>「Ah... ah... I mustn't...」</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2020,8 +2018,8 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>Yeah... if it's Rurichiyo-chan, you'd think that,
-wouldn't you？</t>
+          <t>Yeah... if it's Rurichiyo-chan, you'd end up thinking
+that, wouldn't you?</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2036,7 +2034,7 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>But that will become a new step...</t>
+          <t>But that will be a new step...</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2051,8 +2049,8 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>Thinking about that makes me sentimental, but
-Rurichiyo-chan was bolder than I thought.</t>
+          <t>Thinking about that made me feel sentimental, but
+Rurichiyo-chan was bolder than I had expected.</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2067,7 +2065,7 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2082,7 +2080,7 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nn, nn！ Nfuah—nngh！」</t>
+          <t>「Nn... nng, nng! Nfuh~... nng!」</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2097,9 +2095,9 @@
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>No, you mustn't, she said, and right after that, I
-pressed the smartphone even harder against her
-between (my/her) legs.</t>
+          <t>"No, you mustn't," she said — and no sooner had she
+said that, I pressed the smartphone even harder
+between her legs.</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2144,8 +2142,8 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>...On closer look, is she using the corner of her
-smartphone to rub at Wareme-san in little circles...？</t>
+          <t>...On closer look, she's using the corner of her
+smartphone to press and rub at Wareme-san...?</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2176,8 +2174,9 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>It looks like she couldn't hold back and moved on to
-the next step... that's the impression I get.</t>
+          <t>It looked like Rurichiyo-chan couldn't hold back and
+had moved on to the next step... that's how it
+seemed.</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2207,7 +2206,7 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>「Hah！ Nn！ Nn, nn...！ Huu...！」</t>
+          <t>Fuh! Nn! Nn, nn...! Fuu...!</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2238,8 +2237,8 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>Inside Rurichiyo-chan, her knowledge and experience
-are probably aligning.</t>
+          <t>Rurichiyo-chan's knowledge and experience are
+probably coming together.</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2285,7 +2284,7 @@
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>「…!  Huh…! Nn! Nn… huff! Huff… nn… fwaa…!」</t>
+          <t>「…! Ah... nn! Nn... fuu! Fuu... nn... fwah...!」</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2347,7 +2346,7 @@
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>Ah… my phone…！</t>
+          <t>Ah... my smartphone...!</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2409,7 +2408,7 @@
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>「Huff... nn, nnn... huh, huh...」</t>
+          <t>「Fuh... nn, nnn... fuh, fuh...!」</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2470,8 +2469,8 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>However, Rurichiyo-chan looked down sadly, and
-timidly moved her smartphone away from between her
+          <t>However, Rurichiyo-chan looked down sadly and,
+hesitantly, moved my smartphone away from between her
 legs.</t>
         </is>
       </c>
@@ -2487,8 +2486,8 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>As in the manga, rubbing between my legs feels
-good…….</t>
+          <t>Just like in the manga, rubbing between her legs
+feels good…….</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2504,8 +2503,8 @@
       <c r="B132" s="1" t="inlineStr">
         <is>
           <t>I get that, but it seems to have stopped
-Rurichiyo-chan’s original seriousness and modesty
-from making her feel good.</t>
+Rurichiyo-chan’s natural seriousness and modesty from
+turning into pleasure.</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2551,7 +2550,7 @@
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>「...u！ Hff, nng...！」</t>
+          <t>「…! Uu... fuu, nn...!」</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2567,7 +2566,7 @@
       <c r="B136" s="1" t="inlineStr">
         <is>
           <t>Rurichiyo-chan let out a sigh that carried a
-different intention than before.</t>
+different intent than before.</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2582,8 +2581,8 @@
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>Then she put her phone back where it was and
-hurriedly turned on her heel.</t>
+          <t>Then she put my smartphone back where it had been and
+hurriedly turned on her heels.</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2643,7 +2642,7 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>Crap... there's nowhere to hide！？</t>
+          <t>Crap... There's nowhere to hide!?</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2704,8 +2703,8 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>...I had no choice, so I pressed myself against the
-shadow of the door.</t>
+          <t>...I had no choice; I pressed myself into the shadow
+by the door.</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2735,7 +2734,7 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>「...........！」</t>
+          <t>「…!」</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2826,7 +2825,7 @@
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>I watched her retreating figure in a daze.</t>
+          <t>I stood there, dumbfounded, watching her walk away.</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2857,8 +2856,8 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>I guess she must have had some internal conflict born
-of being so earnest.</t>
+          <t>As I thought, Rurichiyo-chan must have had an
+internal conflict born of her earnestness.</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2873,8 +2872,7 @@
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>…Still, she’s grown up a little as a girl, hasn’t
-she.</t>
+          <t>…But she’s matured a bit as a girl, hasn’t she?</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2920,7 +2918,7 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>「………………it's not here」</t>
+          <t>「………………It's not here.」</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2982,8 +2980,8 @@
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>She was pretty embarrassed, so I can’t really blame
-her.</t>
+          <t>Rurichiyo-chan was pretty embarrassed, so I can’t
+really blame her.</t>
         </is>
       </c>
       <c r="C163" t="n">
